--- a/Utilities/Powershell Utilities/ProcessComplete/Boeing_Export_20251121V1.xlsx
+++ b/Utilities/Powershell Utilities/ProcessComplete/Boeing_Export_20251121V1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\williamt\source\skillsinc\skills-inc-org\SQL-Projects\Utilities\Powershell Utilities\Process\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006BC677-8C6B-4E0E-BAB7-B89B83499895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFFA069B-89D1-416A-B84A-0110E8C3C487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E5B64DFC-E162-4121-A66B-0F94011EB371}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ED2743EC-8815-462C-B0E0-80A2EEF7CE43}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1878,7 +1878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7720F79-4A0B-4D88-896F-BB1D92275E52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C666EA11-F7C5-4FFF-AFD5-8C40754B7110}">
   <dimension ref="A1:M170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
